--- a/大會師總戰報_20260611/🎨_全策略大會師總表_20260611.xlsx
+++ b/大會師總戰報_20260611/🎨_全策略大會師總表_20260611.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,43 +478,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6469.TWO</t>
+          <t>6186.TWO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>新潤</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
+          <t>四均線起漲精選 | 回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>76.90000000000001</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2013</v>
+        <v>3498</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5410.TWO</t>
+          <t>2348.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>國眾</t>
+          <t>海悅</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -523,13 +523,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44.15</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>8.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="F3" t="n">
-        <v>6520</v>
+        <v>5857</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -540,151 +540,151 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6156.TWO</t>
+          <t>6180.TWO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>松上</t>
+          <t>橘子</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>四均線起漲精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.45</v>
+        <v>47.05</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="F4" t="n">
-        <v>4374</v>
+        <v>2457</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>2913.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>農林</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>333</v>
+        <v>11.45</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="F5" t="n">
-        <v>17412</v>
+        <v>12401</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1101.TW</t>
+          <t>2537.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>聯上發</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>四均線起漲精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.25</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="F6" t="n">
-        <v>31932</v>
+        <v>9520</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1227.TW</t>
+          <t>5508.TWO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>永信建</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28.85</v>
+        <v>57.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="n">
-        <v>2722</v>
+        <v>2885</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1785.TWO</t>
+          <t>1736.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>光洋科</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>145.5</v>
+        <v>112</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>31409</v>
+        <v>1170</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -695,27 +695,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2108.TW</t>
+          <t>1225.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南帝</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29.95</v>
+        <v>30.35</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>2498</v>
+        <v>525</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -726,27 +726,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2637.TW</t>
+          <t>2243.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>宏旭-KY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78.3</v>
+        <v>30.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="F10" t="n">
-        <v>7246</v>
+        <v>2117</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -757,27 +757,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>2208.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>台船</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>226</v>
+        <v>17.85</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>22509</v>
+        <v>2639</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -788,27 +788,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2419.TW</t>
+          <t>2530.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>仲琦</t>
+          <t>華建</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28.6</v>
+        <v>20.25</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1667</v>
+        <v>2282</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -819,12 +819,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2362.TW</t>
+          <t>2540.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>藍天</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48.5</v>
+        <v>55.3</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>6213</v>
+        <v>4166</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -850,12 +850,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5258.TW</t>
+          <t>2548.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>華固</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -864,13 +864,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>50.6</v>
+        <v>105.5</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>998</v>
+        <v>8357</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -881,27 +881,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4533.TWO</t>
+          <t>3576.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>協易機</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30.15</v>
+        <v>18.25</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="F15" t="n">
-        <v>1158</v>
+        <v>57019</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -912,12 +912,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3276.TWO</t>
+          <t>3710.TWO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>宇環</t>
+          <t>連展投控</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>5.99</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>655</v>
+        <v>602</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -943,12 +943,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3003.TW</t>
+          <t>2413.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>健和興</t>
+          <t>環科</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>59.6</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="n">
-        <v>2624</v>
+        <v>21164</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -974,12 +974,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6174.TWO</t>
+          <t>2528.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>皇普</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51.7</v>
+        <v>22.35</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>8266</v>
+        <v>1427</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1005,27 +1005,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6259.TWO</t>
+          <t>1795.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>美時</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29.75</v>
+        <v>202</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>4595</v>
+        <v>2443</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1036,12 +1036,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6510.TWO</t>
+          <t>4560.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>強信-KY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3390</v>
+        <v>32.45</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>738</v>
+        <v>544</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6515.TW</t>
+          <t>4123.TWO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8720</v>
+        <v>37.95</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>552</v>
+        <v>2141</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6550.TW</t>
+          <t>4119.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>旭富</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.45</v>
+        <v>42.95</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1486</v>
+        <v>714</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -1129,12 +1129,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8011.TW</t>
+          <t>4564.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>元翎</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.95</v>
+        <v>15.15</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>957</v>
+        <v>912</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1160,27 +1160,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8071.TWO</t>
+          <t>4934.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.95</v>
+        <v>16.25</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>9600</v>
+        <v>1898</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1191,31 +1191,341 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9914.TW</t>
+          <t>5213.TWO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>亞昕</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>73.7</v>
+        <v>23.7</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="F25" t="n">
-        <v>4777</v>
+        <v>1311</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4745.TWO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>合富-KY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1247</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4714.TWO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>永捷</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1840</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5521.TW</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>工信</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10131</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5258.TW</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>虹堡</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>605</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5534.TW</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>長虹</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>四均線起漲精選</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7305</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7717.TWO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>萊德光電-KY</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>654</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>637</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7788.TW</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>松川精密</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3199</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8034.TWO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>榮群</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>515</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8476.TW</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>台境*</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2789</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9940.TW</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>信義</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>四均線起漲精選</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2242</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
         <v>1</v>
       </c>
     </row>
